--- a/java/springboot/spring_boot_autoconfigure.xlsx
+++ b/java/springboot/spring_boot_autoconfigure.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564"/>
+    <workbookView windowWidth="22368" windowHeight="9564" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="org.springframework.boot.autoco" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="132">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FF2C4557"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>org.springframework.boot.autoconfigure.amqp</t>
+    </r>
+  </si>
   <si>
     <r>
       <rPr>
@@ -30,13 +43,7 @@
     </r>
   </si>
   <si>
-    <t>AutoConfigurationImportFilter</t>
-  </si>
-  <si>
-    <t>AutoConfigurationImportListener</t>
-  </si>
-  <si>
-    <t>AutoConfigurationMetadata</t>
+    <t>RabbitRetryTemplateCustomizer</t>
   </si>
   <si>
     <r>
@@ -51,28 +58,109 @@
     </r>
   </si>
   <si>
-    <t>AbstractDependsOnBeanFactoryPostProcessor</t>
-  </si>
-  <si>
-    <t>AutoConfigurationExcludeFilter</t>
-  </si>
-  <si>
-    <t>AutoConfigurationImportEvent</t>
-  </si>
-  <si>
-    <t>AutoConfigurationImportSelector</t>
-  </si>
-  <si>
-    <t>AutoConfigurationImportSelector.AutoConfigurationEntry</t>
-  </si>
-  <si>
-    <t>AutoConfigurationPackages</t>
-  </si>
-  <si>
-    <t>AutoConfigurations</t>
-  </si>
-  <si>
-    <t>BackgroundPreinitializer</t>
+    <t>AbstractRabbitListenerContainerFactoryConfigurer</t>
+  </si>
+  <si>
+    <t>DirectRabbitListenerContainerFactoryConfigurer</t>
+  </si>
+  <si>
+    <t>RabbitAutoConfiguration</t>
+  </si>
+  <si>
+    <t>RabbitAutoConfiguration.MessagingTemplateConfiguration</t>
+  </si>
+  <si>
+    <t>RabbitAutoConfiguration.RabbitConnectionFactoryCreator</t>
+  </si>
+  <si>
+    <t>RabbitAutoConfiguration.RabbitTemplateConfiguration</t>
+  </si>
+  <si>
+    <t>RabbitProperties</t>
+  </si>
+  <si>
+    <t>RabbitProperties.AmqpContainer</t>
+  </si>
+  <si>
+    <t>RabbitProperties.Cache</t>
+  </si>
+  <si>
+    <t>RabbitProperties.Cache.Channel</t>
+  </si>
+  <si>
+    <t>RabbitProperties.Cache.Connection</t>
+  </si>
+  <si>
+    <t>RabbitProperties.DirectContainer</t>
+  </si>
+  <si>
+    <t>RabbitProperties.Listener</t>
+  </si>
+  <si>
+    <t>RabbitProperties.ListenerRetry</t>
+  </si>
+  <si>
+    <t>RabbitProperties.Retry</t>
+  </si>
+  <si>
+    <t>RabbitProperties.SimpleContainer</t>
+  </si>
+  <si>
+    <t>RabbitProperties.Template</t>
+  </si>
+  <si>
+    <t>RabbitTemplateConfigurer</t>
+  </si>
+  <si>
+    <t>SimpleRabbitListenerContainerFactoryConfigurer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.75"/>
+        <color rgb="FF353833"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Enums</t>
+    </r>
+  </si>
+  <si>
+    <t>RabbitProperties.ContainerType</t>
+  </si>
+  <si>
+    <t>RabbitRetryTemplateCustomizer.Target</t>
+  </si>
+  <si>
+    <t>BasicBatchConfigurer</t>
+  </si>
+  <si>
+    <t>BatchAutoConfiguration</t>
+  </si>
+  <si>
+    <t>BatchDataSourceInitializer</t>
+  </si>
+  <si>
+    <t>BatchProperties</t>
+  </si>
+  <si>
+    <t>BatchProperties.Job</t>
+  </si>
+  <si>
+    <t>JobExecutionEvent</t>
+  </si>
+  <si>
+    <t>JobExecutionExitCodeGenerator</t>
+  </si>
+  <si>
+    <t>JobLauncherApplicationRunner</t>
+  </si>
+  <si>
+    <t>JobLauncherCommandLineRunner</t>
+  </si>
+  <si>
+    <t>JpaBatchConfigurer</t>
   </si>
   <si>
     <r>
@@ -87,9 +175,177 @@
     </r>
   </si>
   <si>
+    <t>BatchDataSource</t>
+  </si>
+  <si>
+    <t>org.springframework.boot.autoconfigure</t>
+  </si>
+  <si>
+    <t>org.springframework.boot.autoconfigure.jdbc</t>
+  </si>
+  <si>
+    <t>org.springframework.boot.autoconfigure.amqp</t>
+  </si>
+  <si>
+    <t>org.springframework.boot.autoconfigure.batch</t>
+  </si>
+  <si>
+    <t>AutoConfigurationImportFilter</t>
+  </si>
+  <si>
+    <t>DataSourceAutoConfiguration</t>
+  </si>
+  <si>
+    <t>CacheManagerCustomizer</t>
+  </si>
+  <si>
+    <t>CqlSessionBuilderCustomizer</t>
+  </si>
+  <si>
+    <t>AutoConfigurationImportListener</t>
+  </si>
+  <si>
+    <t>DataSourceAutoConfiguration.EmbeddedDatabaseConfiguration</t>
+  </si>
+  <si>
+    <t>CouchbaseCacheManagerBuilderCustomizer</t>
+  </si>
+  <si>
+    <t>DriverConfigLoaderBuilderCustomizer</t>
+  </si>
+  <si>
+    <t>AutoConfigurationMetadata</t>
+  </si>
+  <si>
+    <t>DataSourceAutoConfiguration.PooledDataSourceConfiguration</t>
+  </si>
+  <si>
+    <t>JCacheManagerCustomizer</t>
+  </si>
+  <si>
+    <t>DataSourceProperties</t>
+  </si>
+  <si>
+    <t>RedisCacheManagerBuilderCustomizer</t>
+  </si>
+  <si>
+    <t>DataSourceProperties.Xa</t>
+  </si>
+  <si>
+    <t>DataSourceSchemaCreatedEvent</t>
+  </si>
+  <si>
+    <t>CassandraAutoConfiguration</t>
+  </si>
+  <si>
+    <t>AbstractDependsOnBeanFactoryPostProcessor</t>
+  </si>
+  <si>
+    <t>DataSourceTransactionManagerAutoConfiguration</t>
+  </si>
+  <si>
+    <t>CassandraProperties</t>
+  </si>
+  <si>
+    <t>AutoConfigurationExcludeFilter</t>
+  </si>
+  <si>
+    <t>EmbeddedDataSourceConfiguration</t>
+  </si>
+  <si>
+    <t>CacheAutoConfiguration</t>
+  </si>
+  <si>
+    <t>CassandraProperties.Connection</t>
+  </si>
+  <si>
+    <t>AutoConfigurationImportEvent</t>
+  </si>
+  <si>
+    <t>JdbcOperationsDependsOnPostProcessor</t>
+  </si>
+  <si>
+    <t>CacheManagerCustomizers</t>
+  </si>
+  <si>
+    <t>CassandraProperties.Pool</t>
+  </si>
+  <si>
+    <t>AutoConfigurationImportSelector</t>
+  </si>
+  <si>
+    <t>JdbcProperties</t>
+  </si>
+  <si>
+    <t>CacheProperties</t>
+  </si>
+  <si>
+    <t>CassandraProperties.Request</t>
+  </si>
+  <si>
+    <t>AutoConfigurationImportSelector.AutoConfigurationEntry</t>
+  </si>
+  <si>
+    <t>JdbcProperties.Template</t>
+  </si>
+  <si>
+    <t>CacheProperties.Caffeine</t>
+  </si>
+  <si>
+    <t>CassandraProperties.Throttler</t>
+  </si>
+  <si>
+    <t>AutoConfigurationPackages</t>
+  </si>
+  <si>
+    <t>JdbcTemplateAutoConfiguration</t>
+  </si>
+  <si>
+    <t>CacheProperties.Couchbase</t>
+  </si>
+  <si>
+    <t>AutoConfigurations</t>
+  </si>
+  <si>
+    <t>JndiDataSourceAutoConfiguration</t>
+  </si>
+  <si>
+    <t>CacheProperties.EhCache</t>
+  </si>
+  <si>
+    <t>BackgroundPreinitializer</t>
+  </si>
+  <si>
+    <t>NamedParameterJdbcOperationsDependsOnPostProcessor</t>
+  </si>
+  <si>
+    <t>CacheProperties.Infinispan</t>
+  </si>
+  <si>
+    <t>XADataSourceAutoConfiguration</t>
+  </si>
+  <si>
+    <t>CacheProperties.JCache</t>
+  </si>
+  <si>
+    <t>CassandraProperties.Compression</t>
+  </si>
+  <si>
+    <t>CacheProperties.Redis</t>
+  </si>
+  <si>
+    <t>CassandraProperties.ThrottlerType</t>
+  </si>
+  <si>
+    <t>CouchbaseCacheConfiguration</t>
+  </si>
+  <si>
     <t>AutoConfigurationPackage</t>
   </si>
   <si>
+    <t>InfinispanCacheConfiguration</t>
+  </si>
+  <si>
     <t>AutoConfigureAfter</t>
   </si>
   <si>
@@ -102,133 +358,106 @@
     <t>EnableAutoConfiguration</t>
   </si>
   <si>
+    <t>CacheType</t>
+  </si>
+  <si>
     <t>ImportAutoConfiguration</t>
   </si>
   <si>
     <t>SpringBootApplication</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color rgb="FF2C4557"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>org.springframework.boot.autoconfigure.amqp</t>
-    </r>
-  </si>
-  <si>
-    <t>RabbitRetryTemplateCustomizer</t>
-  </si>
-  <si>
-    <t>AbstractRabbitListenerContainerFactoryConfigurer</t>
-  </si>
-  <si>
-    <t>DirectRabbitListenerContainerFactoryConfigurer</t>
-  </si>
-  <si>
-    <t>RabbitAutoConfiguration</t>
-  </si>
-  <si>
-    <t>RabbitAutoConfiguration.MessagingTemplateConfiguration</t>
-  </si>
-  <si>
-    <t>RabbitAutoConfiguration.RabbitConnectionFactoryCreator</t>
-  </si>
-  <si>
-    <t>RabbitAutoConfiguration.RabbitTemplateConfiguration</t>
-  </si>
-  <si>
-    <t>RabbitProperties</t>
-  </si>
-  <si>
-    <t>RabbitProperties.AmqpContainer</t>
-  </si>
-  <si>
-    <t>RabbitProperties.Cache</t>
-  </si>
-  <si>
-    <t>RabbitProperties.Cache.Channel</t>
-  </si>
-  <si>
-    <t>RabbitProperties.Cache.Connection</t>
-  </si>
-  <si>
-    <t>RabbitProperties.DirectContainer</t>
-  </si>
-  <si>
-    <t>RabbitProperties.Listener</t>
-  </si>
-  <si>
-    <t>RabbitProperties.ListenerRetry</t>
-  </si>
-  <si>
-    <t>RabbitProperties.Retry</t>
-  </si>
-  <si>
-    <t>RabbitProperties.SimpleContainer</t>
-  </si>
-  <si>
-    <t>RabbitProperties.Template</t>
-  </si>
-  <si>
-    <t>RabbitTemplateConfigurer</t>
-  </si>
-  <si>
-    <t>SimpleRabbitListenerContainerFactoryConfigurer</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9.75"/>
-        <color rgb="FF353833"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Enums</t>
-    </r>
-  </si>
-  <si>
-    <t>RabbitProperties.ContainerType</t>
-  </si>
-  <si>
-    <t>RabbitRetryTemplateCustomizer.Target</t>
-  </si>
-  <si>
-    <t>BasicBatchConfigurer</t>
-  </si>
-  <si>
-    <t>BatchAutoConfiguration</t>
-  </si>
-  <si>
-    <t>BatchDataSourceInitializer</t>
-  </si>
-  <si>
-    <t>BatchProperties</t>
-  </si>
-  <si>
-    <t>BatchProperties.Job</t>
-  </si>
-  <si>
-    <t>JobExecutionEvent</t>
-  </si>
-  <si>
-    <t>JobExecutionExitCodeGenerator</t>
-  </si>
-  <si>
-    <t>JobLauncherApplicationRunner</t>
-  </si>
-  <si>
-    <t>JobLauncherCommandLineRunner</t>
-  </si>
-  <si>
-    <t>JpaBatchConfigurer</t>
-  </si>
-  <si>
-    <t>BatchDataSource</t>
+    <t>AbstractNestedCondition</t>
+  </si>
+  <si>
+    <t>AbstractNestedCondition.MemberMatchOutcomes</t>
+  </si>
+  <si>
+    <t>AllNestedConditions</t>
+  </si>
+  <si>
+    <t>AnyNestedCondition</t>
+  </si>
+  <si>
+    <t>ConditionEvaluationReport</t>
+  </si>
+  <si>
+    <t>ConditionEvaluationReport.ConditionAndOutcome</t>
+  </si>
+  <si>
+    <t>ConditionEvaluationReport.ConditionAndOutcomes</t>
+  </si>
+  <si>
+    <t>ConditionMessage</t>
+  </si>
+  <si>
+    <t>ConditionOutcome</t>
+  </si>
+  <si>
+    <t>NoneNestedConditions</t>
+  </si>
+  <si>
+    <t>OnPropertyListCondition</t>
+  </si>
+  <si>
+    <t>ResourceCondition</t>
+  </si>
+  <si>
+    <t>SpringBootCondition</t>
+  </si>
+  <si>
+    <t>ConditionalOnJava.Range</t>
+  </si>
+  <si>
+    <t>ConditionalOnWebApplication.Type</t>
+  </si>
+  <si>
+    <t>ConditionMessage.Style</t>
+  </si>
+  <si>
+    <t>SearchStrategy</t>
+  </si>
+  <si>
+    <t>ConditionalOnBean</t>
+  </si>
+  <si>
+    <t>ConditionalOnClass</t>
+  </si>
+  <si>
+    <t>ConditionalOnCloudPlatform</t>
+  </si>
+  <si>
+    <t>ConditionalOnExpression</t>
+  </si>
+  <si>
+    <t>ConditionalOnJava</t>
+  </si>
+  <si>
+    <t>ConditionalOnJndi</t>
+  </si>
+  <si>
+    <t>ConditionalOnMissingBean</t>
+  </si>
+  <si>
+    <t>ConditionalOnMissingClass</t>
+  </si>
+  <si>
+    <t>ConditionalOnNotWebApplication</t>
+  </si>
+  <si>
+    <t>ConditionalOnProperty</t>
+  </si>
+  <si>
+    <t>ConditionalOnResource</t>
+  </si>
+  <si>
+    <t>ConditionalOnSingleCandidate</t>
+  </si>
+  <si>
+    <t>ConditionalOnWarDeployment</t>
+  </si>
+  <si>
+    <t>ConditionalOnWebApplication</t>
   </si>
 </sst>
 </file>
@@ -241,7 +470,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,21 +480,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color rgb="FF2C4557"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9.75"/>
       <color rgb="FF353833"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF4A6782"/>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF2C4557"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -722,10 +945,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -734,33 +957,36 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -770,97 +996,94 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -874,8 +1097,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1196,115 +1419,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="1" max="1" width="81.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" ht="19.2" spans="1:1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1316,140 +1564,80 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="81.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="80.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
+      <c r="A3" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>31</v>
+      <c r="A16" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1461,96 +1649,558 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="80.3333333333333" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.2" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="4:20">
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>54</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="4:20">
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>67</v>
+      </c>
+      <c r="T10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>71</v>
+      </c>
+      <c r="T11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>75</v>
+      </c>
+      <c r="T12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" ht="25.2" spans="1:17">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="4:20">
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>87</v>
+      </c>
+      <c r="T16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" ht="25.2" spans="1:20">
+      <c r="A17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>89</v>
+      </c>
+      <c r="T17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="10:17">
+      <c r="J18" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23" t="s">
         <v>21</v>
       </c>
+      <c r="Q23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>99</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="10:10">
+      <c r="J26" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="10:10">
+      <c r="J28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="10:10">
+      <c r="J29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:A38"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
-        <v>45</v>
+      <c r="A5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
-        <v>46</v>
+      <c r="A6" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
-        <v>47</v>
+      <c r="A7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="3" t="s">
-        <v>48</v>
+      <c r="A8" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
-        <v>49</v>
+      <c r="A9" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="3" t="s">
-        <v>50</v>
+      <c r="A10" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
-        <v>51</v>
+      <c r="A11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="3" t="s">
-        <v>52</v>
+      <c r="A12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="3" t="s">
-        <v>53</v>
+      <c r="A13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="3" t="s">
-        <v>54</v>
+      <c r="A14" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="2" t="s">
-        <v>13</v>
+      <c r="A16" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
-        <v>55</v>
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" ht="25.2" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" display="BasicBatchConfigurer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/BasicBatchConfigurer.html"/>
-    <hyperlink ref="A6" r:id="rId2" display="BatchAutoConfiguration" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/BatchAutoConfiguration.html"/>
-    <hyperlink ref="A7" r:id="rId3" display="BatchDataSourceInitializer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/BatchDataSourceInitializer.html"/>
-    <hyperlink ref="A8" r:id="rId4" display="BatchProperties" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/BatchProperties.html"/>
-    <hyperlink ref="A9" r:id="rId5" display="BatchProperties.Job" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/BatchProperties.Job.html"/>
-    <hyperlink ref="A10" r:id="rId6" display="JobExecutionEvent" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/JobExecutionEvent.html"/>
-    <hyperlink ref="A11" r:id="rId7" display="JobExecutionExitCodeGenerator" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/JobExecutionExitCodeGenerator.html"/>
-    <hyperlink ref="A12" r:id="rId8" display="JobLauncherApplicationRunner" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/JobLauncherApplicationRunner.html"/>
-    <hyperlink ref="A13" r:id="rId9" display="JobLauncherCommandLineRunner" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/JobLauncherCommandLineRunner.html"/>
-    <hyperlink ref="A14" r:id="rId10" display="JpaBatchConfigurer" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/JpaBatchConfigurer.html"/>
-    <hyperlink ref="A18" r:id="rId11" display="BatchDataSource" tooltip="https://docs.spring.io/spring-boot/docs/2.3.x/api/org/springframework/boot/autoconfigure/batch/BatchDataSource.html"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
